--- a/output/pdf_financials_xlsx/RDS.xlsx
+++ b/output/pdf_financials_xlsx/RDS.xlsx
@@ -1092,28 +1092,28 @@
         </is>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.013781</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.015697</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.044209</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>-0.131056</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>-0.06350500000000001</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>-0.14774</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>-0.363658</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>-0.441242</v>
       </c>
     </row>
     <row r="13">
@@ -2140,28 +2140,28 @@
         </is>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.558879</v>
+        <v>-0.5726599999999999</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.9038620000000001</v>
+        <v>-0.919559</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.85943</v>
+        <v>-0.903639</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-1.388946</v>
+        <v>-1.25789</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-3.448885</v>
+        <v>-3.38538</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-1.525656</v>
+        <v>-1.377916</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-2.137194</v>
+        <v>-1.773536</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-2.722351</v>
+        <v>-2.281109</v>
       </c>
     </row>
     <row r="28">
@@ -2264,28 +2264,28 @@
         </is>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.558879</v>
+        <v>-0.5726599999999999</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.9038620000000001</v>
+        <v>-0.919559</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.85943</v>
+        <v>-0.903639</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-1.388946</v>
+        <v>-1.25789</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-3.448885</v>
+        <v>-3.38538</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-1.525656</v>
+        <v>-1.377916</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-2.137194</v>
+        <v>-1.773536</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-2.722351</v>
+        <v>-2.281109</v>
       </c>
     </row>
     <row r="30">
@@ -2334,28 +2334,28 @@
         </is>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-1703.172426403365</v>
+        <v>-1745.169744621198</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-4992.885157156273</v>
+        <v>-5079.594542341049</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-1944.015924359293</v>
+        <v>-2044.015924359293</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>166.4361155248154</v>
+        <v>150.7317961659489</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>-303.4667992380081</v>
+        <v>-297.8790051870004</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>5456.56652360515</v>
+        <v>4928.168812589413</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>58425.20503007107</v>
+        <v>48483.76161837069</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>399.6158486998747</v>
+        <v>334.8456202054483</v>
       </c>
     </row>
     <row r="31">
@@ -2504,19 +2504,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.159809</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.071321</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.071321</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.061675</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>0</v>
@@ -2546,13 +2546,13 @@
         <v>3.083512</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>1.91692</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>8.398031</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>20.099648</v>
       </c>
     </row>
     <row r="35">
@@ -2620,19 +2620,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.159809</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.071321</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.071321</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.061675</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>0</v>
@@ -2662,13 +2662,13 @@
         <v>3.083512</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>1.91692</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>8.398031</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>20.099648</v>
       </c>
     </row>
     <row r="37">
@@ -3322,13 +3322,13 @@
         <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.08496099999999999</v>
+        <v>0.01364</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0.671949</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.367966</v>
+        <v>0.306291</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>0.189272</v>
@@ -3358,13 +3358,13 @@
         <v>1.080551</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>9.027609999999999</v>
+        <v>7.11069</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>8.849519000000001</v>
+        <v>0.451488</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>34.367528</v>
+        <v>14.26788</v>
       </c>
     </row>
     <row r="49">
@@ -8950,7 +8950,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -18671,7 +18671,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -20600,7 +20600,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -22428,7 +22428,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E143" s="5" t="n">
@@ -41503,7 +41503,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
@@ -42972,7 +42972,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
@@ -44970,7 +44970,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">

--- a/output/pdf_financials_xlsx/RDS.xlsx
+++ b/output/pdf_financials_xlsx/RDS.xlsx
@@ -875,13 +875,13 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>0.030873</v>
+        <v>0.036273</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0.022883</v>
+        <v>0.027683</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.018164</v>
+        <v>0.022964</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>0</v>
@@ -937,13 +937,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.031977</v>
+        <v>0.037377</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.023901</v>
+        <v>0.028701</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.019148</v>
+        <v>0.023948</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>0</v>
@@ -999,13 +999,13 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>0.054364</v>
+        <v>0.048964</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0.038541</v>
+        <v>0.033741</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0.113248</v>
+        <v>0.108448</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>0</v>
@@ -2183,7 +2183,7 @@
         <v>0</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
+        <v>0.002059</v>
       </c>
       <c r="G28" s="1" t="inlineStr">
         <is>
@@ -2191,10 +2191,10 @@
         </is>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0</v>
+        <v>0.002062</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0</v>
+        <v>0.001906</v>
       </c>
       <c r="J28" s="1" t="inlineStr">
         <is>
@@ -2202,28 +2202,28 @@
         </is>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
+        <v>0.003088</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0</v>
+        <v>0.00391</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0</v>
+        <v>0.003966</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0</v>
+        <v>0.067885</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0</v>
+        <v>0.166259</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0</v>
+        <v>0.12002</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>0</v>
+        <v>0.101081</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>0</v>
+        <v>0.11087</v>
       </c>
     </row>
     <row r="29">
@@ -2245,7 +2245,7 @@
         <v>-0.839632</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.261209</v>
+        <v>-0.25915</v>
       </c>
       <c r="G29" s="1" t="inlineStr">
         <is>
@@ -2253,10 +2253,10 @@
         </is>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.239687</v>
+        <v>-0.237625</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.556285</v>
+        <v>-0.554379</v>
       </c>
       <c r="J29" s="1" t="inlineStr">
         <is>
@@ -2264,28 +2264,28 @@
         </is>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.5726599999999999</v>
+        <v>-0.569572</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.919559</v>
+        <v>-0.915649</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.903639</v>
+        <v>-0.8996729999999999</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-1.25789</v>
+        <v>-1.190005</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-3.38538</v>
+        <v>-3.219121</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-1.377916</v>
+        <v>-1.257896</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-1.773536</v>
+        <v>-1.672455</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-2.281109</v>
+        <v>-2.170239</v>
       </c>
     </row>
     <row r="30">
@@ -2334,28 +2334,28 @@
         </is>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-1745.169744621198</v>
+        <v>-1735.759127201804</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-5079.594542341049</v>
+        <v>-5057.995912279733</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-2044.015924359293</v>
+        <v>-2035.044900359655</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>150.7317961659489</v>
+        <v>142.5971993548403</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>-297.8790051870004</v>
+        <v>-283.2499043110616</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>4928.168812589413</v>
+        <v>4498.912732474964</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>48483.76161837069</v>
+        <v>45720.4756697649</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>334.8456202054483</v>
+        <v>318.5709336770193</v>
       </c>
     </row>
     <row r="31">
@@ -6395,7 +6395,7 @@
         </is>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.002059</v>
       </c>
       <c r="G100" s="1" t="inlineStr">
         <is>
@@ -6403,10 +6403,10 @@
         </is>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>0.002062</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>0.001906</v>
       </c>
       <c r="J100" s="1" t="inlineStr">
         <is>
@@ -6414,28 +6414,28 @@
         </is>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>0.003088</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>0.00391</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>0.003966</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>0.067885</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>0.166259</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>0.12002</v>
       </c>
       <c r="Q100" s="3" t="n">
-        <v>0</v>
+        <v>0.101081</v>
       </c>
       <c r="R100" s="3" t="n">
-        <v>0</v>
+        <v>0.11087</v>
       </c>
     </row>
     <row r="101">
@@ -7191,19 +7191,19 @@
         <v>0</v>
       </c>
       <c r="N112" s="3" t="n">
-        <v>0</v>
+        <v>0.028423</v>
       </c>
       <c r="O112" s="3" t="n">
-        <v>0</v>
+        <v>0.012089</v>
       </c>
       <c r="P112" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q112" s="3" t="n">
-        <v>0</v>
+        <v>0.0045</v>
       </c>
       <c r="R112" s="3" t="n">
-        <v>0</v>
+        <v>0.001138</v>
       </c>
     </row>
     <row r="113">
@@ -25697,7 +25697,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr"/>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E176" t="inlineStr">
         <is>
           <t>-</t>
@@ -25790,7 +25794,11 @@
           <t>Loss on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr"/>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E177" t="inlineStr">
         <is>
           <t>-</t>
@@ -26760,7 +26768,11 @@
           <t>Proceeds on disposition of property and equipment</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr"/>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E187" t="inlineStr">
         <is>
           <t>-</t>
@@ -28730,7 +28742,11 @@
           <t>Proceed from disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr"/>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E207" t="inlineStr">
         <is>
           <t>-</t>
@@ -30005,7 +30021,11 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr"/>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E220" t="inlineStr">
         <is>
           <t>-</t>
@@ -31581,7 +31601,11 @@
           <t>Depreciation of property, plant and equipment 3,088</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr"/>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E236" t="inlineStr">
         <is>
           <t>-</t>
@@ -35710,7 +35734,11 @@
           <t>Depreciation of property, plant and equipment 2,664</t>
         </is>
       </c>
-      <c r="D277" t="inlineStr"/>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E277" t="inlineStr">
         <is>
           <t>-</t>
@@ -41052,7 +41080,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D331" t="inlineStr"/>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E331" t="inlineStr">
         <is>
           <t>-</t>
@@ -43651,7 +43683,11 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D358" t="inlineStr"/>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E358" t="inlineStr">
         <is>
           <t>-</t>
@@ -46297,7 +46333,11 @@
           <t>Depreciation of property, plant and equipment 3,088</t>
         </is>
       </c>
-      <c r="D384" t="inlineStr"/>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E384" t="inlineStr">
         <is>
           <t>-</t>
@@ -48196,7 +48236,11 @@
           <t>Rent and occupancy costs</t>
         </is>
       </c>
-      <c r="D403" t="inlineStr"/>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E403" s="5" t="n">
         <v>0.0054</v>
       </c>
